--- a/vibe-coding-prep/dummy_data/master/종목_운용사_매핑표.xlsx
+++ b/vibe-coding-prep/dummy_data/master/종목_운용사_매핑표.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,30 +735,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>알파 단기채 MMF 1호</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KRZZ00000110</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>감마 세컨더리 PEF 3호</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>KRZZ00000102</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>C30003</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>감마파트너스</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>20260630_C30003_기준가격대장.xlsx</t>
         </is>
